--- a/E/BFD05D.xlsx
+++ b/E/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="730">
   <si>
     <t/>
   </si>
@@ -1345,12 +1345,6 @@
     <t>PT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20115331</t>
-  </si>
-  <si>
-    <t>IDM SANTAN KELAPA 65</t>
-  </si>
-  <si>
     <t>10022118</t>
   </si>
   <si>
@@ -1375,6 +1369,15 @@
     <t>SUN KARA SANTAN 200</t>
   </si>
   <si>
+    <t>20138647</t>
+  </si>
+  <si>
+    <t>SUN KARA TPK 110ML</t>
+  </si>
+  <si>
+    <t>,(E-2B)</t>
+  </si>
+  <si>
     <t>10036806</t>
   </si>
   <si>
@@ -2186,6 +2189,12 @@
   </si>
   <si>
     <t>BIMOLI MYK.GRG REF2L</t>
+  </si>
+  <si>
+    <t>20140636</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL1.5</t>
   </si>
   <si>
     <t>10003974</t>
@@ -2584,7 +2593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6748,10 +6757,10 @@
         <v>442</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>443</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6768,7 +6777,7 @@
         <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6788,10 +6797,10 @@
         <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6808,10 +6817,10 @@
         <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6828,18 +6837,18 @@
         <v>442</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
@@ -6848,7 +6857,7 @@
         <v>442</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6856,10 +6865,10 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
@@ -6868,7 +6877,7 @@
         <v>442</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>23</v>
@@ -6876,10 +6885,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
@@ -6888,7 +6897,7 @@
         <v>442</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -6896,10 +6905,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
@@ -6908,7 +6917,7 @@
         <v>442</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -6916,10 +6925,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
@@ -6928,7 +6937,7 @@
         <v>442</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -6936,10 +6945,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
@@ -6948,7 +6957,7 @@
         <v>442</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -6956,76 +6965,76 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>18</v>
@@ -7036,16 +7045,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>18</v>
@@ -7056,36 +7065,36 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>8</v>
@@ -7096,16 +7105,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
@@ -7116,16 +7125,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -7136,16 +7145,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>26</v>
@@ -7156,16 +7165,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>26</v>
@@ -7176,16 +7185,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>26</v>
@@ -7196,16 +7205,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>29</v>
@@ -7216,16 +7225,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>29</v>
@@ -7236,16 +7245,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>29</v>
@@ -7256,16 +7265,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>11</v>
@@ -7276,16 +7285,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7296,16 +7305,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
@@ -7316,16 +7325,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>34</v>
@@ -7336,16 +7345,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -7356,16 +7365,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>34</v>
@@ -7376,16 +7385,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>15</v>
@@ -7396,16 +7405,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>4</v>
@@ -7416,16 +7425,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>18</v>
@@ -7436,16 +7445,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>8</v>
@@ -7456,16 +7465,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>26</v>
@@ -7476,16 +7485,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>29</v>
@@ -7496,16 +7505,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>11</v>
@@ -7516,16 +7525,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>4</v>
@@ -7536,16 +7545,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>18</v>
@@ -7556,16 +7565,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>8</v>
@@ -7576,16 +7585,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>26</v>
@@ -7596,16 +7605,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>29</v>
@@ -7616,16 +7625,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>11</v>
@@ -7636,16 +7645,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>34</v>
@@ -7656,36 +7665,36 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>94</v>
@@ -7696,16 +7705,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>4</v>
@@ -7716,16 +7725,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>18</v>
@@ -7736,16 +7745,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>8</v>
@@ -7756,16 +7765,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>26</v>
@@ -7776,16 +7785,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>29</v>
@@ -7796,16 +7805,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>11</v>
@@ -7816,36 +7825,36 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>94</v>
@@ -7856,16 +7865,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>97</v>
@@ -7876,16 +7885,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>100</v>
@@ -7896,16 +7905,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>173</v>
@@ -7916,16 +7925,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>176</v>
@@ -7936,16 +7945,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>4</v>
@@ -7956,16 +7965,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>18</v>
@@ -7976,16 +7985,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>8</v>
@@ -7996,16 +8005,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>26</v>
@@ -8016,16 +8025,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>29</v>
@@ -8036,36 +8045,36 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>15</v>
@@ -8076,16 +8085,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>94</v>
@@ -8096,16 +8105,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>4</v>
@@ -8116,16 +8125,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>18</v>
@@ -8136,16 +8145,16 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>8</v>
@@ -8156,16 +8165,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>26</v>
@@ -8176,16 +8185,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>29</v>
@@ -8196,16 +8205,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>11</v>
@@ -8216,16 +8225,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>34</v>
@@ -8236,16 +8245,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>15</v>
@@ -8256,36 +8265,36 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>18</v>
@@ -8296,16 +8305,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>8</v>
@@ -8316,16 +8325,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>26</v>
@@ -8336,16 +8345,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>29</v>
@@ -8356,16 +8365,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>11</v>
@@ -8376,16 +8385,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>34</v>
@@ -8396,16 +8405,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>15</v>
@@ -8416,16 +8425,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>94</v>
@@ -8436,16 +8445,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>97</v>
@@ -8456,16 +8465,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>100</v>
@@ -8476,16 +8485,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>173</v>
@@ -8496,16 +8505,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>176</v>
@@ -8516,16 +8525,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>225</v>
@@ -8536,16 +8545,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>4</v>
@@ -8556,16 +8565,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>18</v>
@@ -8576,16 +8585,16 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>8</v>
@@ -8596,16 +8605,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>26</v>
@@ -8616,16 +8625,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>29</v>
@@ -8636,16 +8645,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>34</v>
@@ -8656,16 +8665,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>15</v>
@@ -8676,16 +8685,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>94</v>
@@ -8696,16 +8705,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>4</v>
@@ -8716,16 +8725,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>18</v>
@@ -8736,16 +8745,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>8</v>
@@ -8756,16 +8765,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>26</v>
@@ -8776,16 +8785,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>29</v>
@@ -8796,16 +8805,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>11</v>
@@ -8816,16 +8825,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>34</v>
@@ -8836,16 +8845,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>15</v>
@@ -8856,16 +8865,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>94</v>
@@ -8876,16 +8885,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>4</v>
@@ -8896,16 +8905,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>672</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>18</v>
@@ -8916,16 +8925,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>8</v>
@@ -8936,16 +8945,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>26</v>
@@ -8956,16 +8965,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>29</v>
@@ -8976,36 +8985,36 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>4</v>
@@ -9016,16 +9025,16 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>18</v>
@@ -9036,16 +9045,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>8</v>
@@ -9056,16 +9065,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>26</v>
@@ -9076,16 +9085,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>29</v>
@@ -9096,16 +9105,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>11</v>
@@ -9116,16 +9125,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>4</v>
@@ -9136,16 +9145,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>18</v>
@@ -9156,16 +9165,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>8</v>
@@ -9176,16 +9185,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>26</v>
@@ -9196,16 +9205,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>29</v>
@@ -9216,16 +9225,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>4</v>
@@ -9236,16 +9245,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>18</v>
@@ -9256,16 +9265,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>8</v>
@@ -9276,16 +9285,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>26</v>
@@ -9296,16 +9305,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>29</v>
@@ -9316,36 +9325,36 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>18</v>
@@ -9356,21 +9365,41 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E339" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="E340" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F339" s="1" t="s">
+      <c r="F340" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/E/BFD05D.xlsx
+++ b/E/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="732">
   <si>
     <t/>
   </si>
@@ -1235,6 +1235,12 @@
   </si>
   <si>
     <t>NUTRI/J PUDNG B/C130</t>
+  </si>
+  <si>
+    <t>20143399</t>
+  </si>
+  <si>
+    <t>NRJL PDG SUSU COCO90</t>
   </si>
   <si>
     <t>20132655</t>
@@ -2593,7 +2599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6440,7 +6446,7 @@
         <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,7 +6526,7 @@
         <v>97</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6534,33 +6540,33 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6574,13 +6580,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,10 +6600,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -6614,13 +6620,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6634,10 +6640,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>12</v>
@@ -6654,33 +6660,33 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>433</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6694,13 +6700,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6714,13 +6720,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6734,33 +6740,33 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>443</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="E208" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6774,10 +6780,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6794,13 +6800,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6814,13 +6820,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6834,33 +6840,33 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>454</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6874,13 +6880,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6894,10 +6900,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -6914,10 +6920,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -6934,10 +6940,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -6954,10 +6960,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -6974,33 +6980,33 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>470</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7014,13 +7020,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7034,13 +7040,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>84</v>
+        <v>472</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7054,7 +7060,7 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>18</v>
@@ -7074,13 +7080,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>470</v>
+        <v>84</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7094,13 +7100,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>84</v>
+        <v>472</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7114,7 +7120,7 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
@@ -7134,13 +7140,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7154,10 +7160,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>5</v>
@@ -7174,7 +7180,7 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>26</v>
@@ -7194,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>26</v>
@@ -7214,10 +7220,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>5</v>
@@ -7234,7 +7240,7 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>29</v>
@@ -7254,7 +7260,7 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>29</v>
@@ -7274,10 +7280,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7294,7 +7300,7 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7314,7 +7320,7 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
@@ -7334,10 +7340,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7354,7 +7360,7 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -7374,7 +7380,7 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>34</v>
@@ -7394,10 +7400,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>5</v>
@@ -7414,33 +7420,33 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>515</v>
+        <v>471</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E242" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7454,10 +7460,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7474,10 +7480,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7494,13 +7500,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7514,13 +7520,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7534,30 +7540,30 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7574,10 +7580,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7594,13 +7600,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7614,13 +7620,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7634,13 +7640,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7654,13 +7660,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7674,33 +7680,33 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>543</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B255" s="1" t="s">
+      <c r="C255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F255" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F255" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7714,30 +7720,30 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>5</v>
@@ -7754,10 +7760,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>5</v>
@@ -7774,13 +7780,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7794,10 +7800,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7814,13 +7820,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7834,33 +7840,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>561</v>
+        <v>84</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F263" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E263" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F263" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7874,13 +7880,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7894,13 +7900,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7914,13 +7920,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7934,10 +7940,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -7954,33 +7960,33 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="E269" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7994,10 +8000,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>84</v>
@@ -8014,10 +8020,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>84</v>
@@ -8034,10 +8040,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>84</v>
@@ -8054,33 +8060,33 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>585</v>
+        <v>84</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F274" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F274" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8094,13 +8100,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8114,30 +8120,30 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>12</v>
@@ -8145,19 +8151,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="B278" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="C278" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="E278" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>12</v>
@@ -8174,10 +8180,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>12</v>
@@ -8194,13 +8200,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8214,10 +8220,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8234,10 +8240,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8254,13 +8260,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8274,33 +8280,33 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>608</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="E285" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F285" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F285" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8314,10 +8320,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>12</v>
@@ -8334,10 +8340,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>12</v>
@@ -8354,10 +8360,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>12</v>
@@ -8374,13 +8380,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8394,13 +8400,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8414,10 +8420,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>12</v>
@@ -8434,10 +8440,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>12</v>
@@ -8454,10 +8460,10 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>12</v>
@@ -8474,13 +8480,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8494,13 +8500,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8514,13 +8520,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8534,13 +8540,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8554,10 +8560,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>12</v>
@@ -8565,22 +8571,22 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="E299" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8594,13 +8600,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8614,10 +8620,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>12</v>
@@ -8634,10 +8640,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>12</v>
@@ -8654,10 +8660,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>12</v>
@@ -8674,10 +8680,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>12</v>
@@ -8694,13 +8700,13 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8714,10 +8720,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8725,19 +8731,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="E307" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8754,10 +8760,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8774,13 +8780,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8794,10 +8800,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>12</v>
@@ -8814,10 +8820,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>12</v>
@@ -8834,10 +8840,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>12</v>
@@ -8854,10 +8860,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>12</v>
@@ -8874,10 +8880,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>12</v>
@@ -8894,10 +8900,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>12</v>
@@ -8905,19 +8911,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>673</v>
-      </c>
       <c r="E316" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>12</v>
@@ -8934,13 +8940,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8954,13 +8960,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>443</v>
+        <v>84</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8974,13 +8980,13 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>12</v>
+        <v>445</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8994,50 +9000,50 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>684</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F321" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="E321" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F321" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9054,13 +9060,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9074,13 +9080,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9094,13 +9100,13 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9114,13 +9120,13 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9134,30 +9140,30 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>700</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9174,10 +9180,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9194,10 +9200,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9214,10 +9220,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>84</v>
@@ -9234,10 +9240,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>84</v>
@@ -9245,19 +9251,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>84</v>
@@ -9274,10 +9280,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>84</v>
@@ -9294,10 +9300,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>84</v>
@@ -9314,13 +9320,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9334,33 +9340,33 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>723</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="E338" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F338" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9374,13 +9380,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9394,12 +9400,32 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E341" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F340" s="1" t="s">
+      <c r="F341" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/E/BFD05D.xlsx
+++ b/E/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="731">
   <si>
     <t/>
   </si>
@@ -1379,9 +1379,6 @@
   </si>
   <si>
     <t>SUN KARA TPK 110ML</t>
-  </si>
-  <si>
-    <t>,(E-2B)</t>
   </si>
   <si>
     <t>10036806</t>
@@ -6866,15 +6863,15 @@
         <v>34</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>456</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
@@ -6891,10 +6888,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
@@ -6911,10 +6908,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
@@ -6931,10 +6928,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
@@ -6951,10 +6948,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
@@ -6971,10 +6968,10 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
@@ -6991,76 +6988,76 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>18</v>
@@ -7071,16 +7068,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
@@ -7091,36 +7088,36 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
@@ -7131,16 +7128,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -7151,16 +7148,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>8</v>
@@ -7171,16 +7168,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>26</v>
@@ -7191,16 +7188,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>26</v>
@@ -7211,16 +7208,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>26</v>
@@ -7231,16 +7228,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>29</v>
@@ -7251,16 +7248,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>29</v>
@@ -7271,16 +7268,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>29</v>
@@ -7291,16 +7288,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7311,16 +7308,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
@@ -7331,16 +7328,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>11</v>
@@ -7351,16 +7348,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -7371,16 +7368,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>34</v>
@@ -7391,16 +7388,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>34</v>
@@ -7411,16 +7408,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>15</v>
@@ -7431,16 +7428,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>4</v>
@@ -7451,16 +7448,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>18</v>
@@ -7471,16 +7468,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>8</v>
@@ -7491,16 +7488,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>26</v>
@@ -7511,16 +7508,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>29</v>
@@ -7531,16 +7528,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>11</v>
@@ -7551,16 +7548,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>4</v>
@@ -7571,16 +7568,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>18</v>
@@ -7591,16 +7588,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>8</v>
@@ -7611,16 +7608,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>26</v>
@@ -7631,16 +7628,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>29</v>
@@ -7651,16 +7648,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>11</v>
@@ -7671,16 +7668,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>34</v>
@@ -7691,36 +7688,36 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>94</v>
@@ -7731,16 +7728,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>4</v>
@@ -7751,16 +7748,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>18</v>
@@ -7771,16 +7768,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>8</v>
@@ -7791,16 +7788,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>556</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>26</v>
@@ -7811,16 +7808,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>29</v>
@@ -7831,16 +7828,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>11</v>
@@ -7851,36 +7848,36 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>94</v>
@@ -7891,16 +7888,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>97</v>
@@ -7911,16 +7908,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>100</v>
@@ -7931,16 +7928,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>173</v>
@@ -7951,16 +7948,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>176</v>
@@ -7971,16 +7968,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>4</v>
@@ -7991,16 +7988,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>18</v>
@@ -8011,16 +8008,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>8</v>
@@ -8031,16 +8028,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>26</v>
@@ -8051,16 +8048,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>29</v>
@@ -8071,36 +8068,36 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>15</v>
@@ -8111,16 +8108,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>591</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>94</v>
@@ -8131,16 +8128,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>4</v>
@@ -8151,16 +8148,16 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>18</v>
@@ -8171,16 +8168,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>8</v>
@@ -8191,16 +8188,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>26</v>
@@ -8211,16 +8208,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>29</v>
@@ -8231,16 +8228,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>11</v>
@@ -8251,16 +8248,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>34</v>
@@ -8271,16 +8268,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>606</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>15</v>
@@ -8291,36 +8288,36 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>18</v>
@@ -8331,16 +8328,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>8</v>
@@ -8351,16 +8348,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>26</v>
@@ -8371,16 +8368,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>29</v>
@@ -8391,16 +8388,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>11</v>
@@ -8411,16 +8408,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>34</v>
@@ -8431,16 +8428,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>15</v>
@@ -8451,16 +8448,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>94</v>
@@ -8471,16 +8468,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>97</v>
@@ -8491,16 +8488,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>100</v>
@@ -8511,16 +8508,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>173</v>
@@ -8531,16 +8528,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>176</v>
@@ -8551,16 +8548,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>225</v>
@@ -8571,16 +8568,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>4</v>
@@ -8591,16 +8588,16 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>18</v>
@@ -8611,16 +8608,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>8</v>
@@ -8631,16 +8628,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>26</v>
@@ -8651,16 +8648,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>29</v>
@@ -8671,16 +8668,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>34</v>
@@ -8691,16 +8688,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>15</v>
@@ -8711,16 +8708,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>94</v>
@@ -8731,16 +8728,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>656</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>4</v>
@@ -8751,16 +8748,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B308" s="1" t="s">
-        <v>658</v>
-      </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>18</v>
@@ -8771,16 +8768,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B309" s="1" t="s">
-        <v>660</v>
-      </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>8</v>
@@ -8791,16 +8788,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>26</v>
@@ -8811,16 +8808,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>664</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>29</v>
@@ -8831,16 +8828,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>666</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>11</v>
@@ -8851,16 +8848,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>34</v>
@@ -8871,16 +8868,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>670</v>
-      </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>15</v>
@@ -8891,16 +8888,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>94</v>
@@ -8911,16 +8908,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>4</v>
@@ -8931,16 +8928,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>677</v>
-      </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>18</v>
@@ -8951,16 +8948,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>679</v>
-      </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>8</v>
@@ -8971,16 +8968,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>681</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>26</v>
@@ -8991,16 +8988,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>29</v>
@@ -9011,36 +9008,36 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>685</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>4</v>
@@ -9051,16 +9048,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>18</v>
@@ -9071,16 +9068,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>8</v>
@@ -9091,16 +9088,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>26</v>
@@ -9111,16 +9108,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>29</v>
@@ -9131,16 +9128,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>11</v>
@@ -9151,16 +9148,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>702</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>4</v>
@@ -9171,16 +9168,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>704</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>18</v>
@@ -9191,16 +9188,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>8</v>
@@ -9211,16 +9208,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>26</v>
@@ -9231,16 +9228,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>29</v>
@@ -9251,16 +9248,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>713</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>4</v>
@@ -9271,16 +9268,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>715</v>
-      </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>18</v>
@@ -9291,16 +9288,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>8</v>
@@ -9311,16 +9308,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>26</v>
@@ -9331,16 +9328,16 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>29</v>
@@ -9351,36 +9348,36 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>18</v>
@@ -9391,16 +9388,16 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>8</v>
@@ -9411,16 +9408,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>26</v>
